--- a/tests/data/missing_required_columns.xlsx
+++ b/tests/data/missing_required_columns.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Budget Bucket</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>Link</t>
         </is>
       </c>
@@ -441,42 +436,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer Bruto Capacity</t>
+          <t>Engineer Capacity (Bruto)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>5</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manager Bruto Capacity</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>http://jira/A</t>
         </is>
